--- a/www/terminologies/ValueSet-jdv-observation-grossesse-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-observation-grossesse-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141838</t>
+    <t>20260220142103</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:38+01:00</t>
+    <t>2026-02-20T14:21:03+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-observation-grossesse-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-observation-grossesse-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142103</t>
+    <t>20260311144902</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:03+01:00</t>
+    <t>2026-03-11T14:49:02+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-observation-grossesse-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-observation-grossesse-cisis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="114">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144902</t>
+    <t>20260420150249</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:02+01:00</t>
+    <t>2026-04-20T15:02:49+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,6 +100,24 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>MED-159</t>
+  </si>
+  <si>
+    <t>Nombre d'enfants pesant moins de 2500 g</t>
+  </si>
+  <si>
+    <t>ORG-173</t>
+  </si>
+  <si>
+    <t>Projet de grossesse</t>
+  </si>
+  <si>
+    <t>MED-280</t>
+  </si>
+  <si>
+    <t>Accouchement récent</t>
+  </si>
+  <si>
     <t>MED-1184</t>
   </si>
   <si>
@@ -112,16 +130,10 @@
     <t>Grossesse extra-utérine</t>
   </si>
   <si>
-    <t>ORG-173</t>
-  </si>
-  <si>
-    <t>Projet de grossesse</t>
-  </si>
-  <si>
-    <t>MED-280</t>
-  </si>
-  <si>
-    <t>Accouchement récent</t>
+    <t>MED-1247</t>
+  </si>
+  <si>
+    <t>Etat du périnée</t>
   </si>
   <si>
     <t/>
@@ -139,6 +151,12 @@
     <t>Poids à la naissance</t>
   </si>
   <si>
+    <t>8348-5</t>
+  </si>
+  <si>
+    <t>Poids corporel avant grossesse</t>
+  </si>
+  <si>
     <t>8665-2</t>
   </si>
   <si>
@@ -265,6 +283,12 @@
     <t>Nombre de grossesses extra-utérines</t>
   </si>
   <si>
+    <t>42797-1</t>
+  </si>
+  <si>
+    <t>Age à la première grossesse</t>
+  </si>
+  <si>
     <t>45371-2</t>
   </si>
   <si>
@@ -277,28 +301,58 @@
     <t>Age gestationnel en semaines</t>
   </si>
   <si>
+    <t>55281-0</t>
+  </si>
+  <si>
+    <t>Nombre de fœtus</t>
+  </si>
+  <si>
     <t>57062-2</t>
   </si>
   <si>
     <t>Nombre d'enfants mort-nés</t>
   </si>
   <si>
+    <t>57071-3</t>
+  </si>
+  <si>
+    <t>Méthode d'accouchement</t>
+  </si>
+  <si>
+    <t>63893-2</t>
+  </si>
+  <si>
+    <t>Issue de la grossesse</t>
+  </si>
+  <si>
     <t>63895-7</t>
   </si>
   <si>
     <t>Allaitement</t>
   </si>
   <si>
-    <t>42797-1</t>
-  </si>
-  <si>
-    <t>Age à la première grossesse</t>
-  </si>
-  <si>
-    <t>55281-0</t>
-  </si>
-  <si>
-    <t>Nombre de fœtus</t>
+    <t>69043-8</t>
+  </si>
+  <si>
+    <t>Nombre de grossesses antérieures</t>
+  </si>
+  <si>
+    <t>75200-6</t>
+  </si>
+  <si>
+    <t>Date de la première consultation (déclaration de grossesse)</t>
+  </si>
+  <si>
+    <t>92276-5</t>
+  </si>
+  <si>
+    <t>Statut du nouveau né</t>
+  </si>
+  <si>
+    <t>93857-1</t>
+  </si>
+  <si>
+    <t>Date et heure de l'accouchement</t>
   </si>
   <si>
     <t>http://loinc.org</t>
@@ -565,7 +619,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -617,15 +671,31 @@
         <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +705,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -652,242 +722,298 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>36</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-jdv-observation-grossesse-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-observation-grossesse-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150249</t>
+    <t>20260619134041</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:49+01:00</t>
+    <t>2026-06-19T13:40:41+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-observation-grossesse-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-observation-grossesse-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134041</t>
+    <t>20260420150249</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:41+01:00</t>
+    <t>2026-04-20T15:02:49+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-observation-grossesse-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-observation-grossesse-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134041</t>
+    <t>20260716085851</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:41+01:00</t>
+    <t>2026-07-16T08:58:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
